--- a/outputs/04_individual_models/mri_results.xlsx
+++ b/outputs/04_individual_models/mri_results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1630" uniqueCount="386">
   <si>
     <t>RID</t>
   </si>
@@ -66,6 +66,9 @@
   </si>
   <si>
     <t>incorrect-high</t>
+  </si>
+  <si>
+    <t>outcome</t>
   </si>
   <si>
     <t>HIGH_conf(&gt;=0.8)</t>
@@ -7628,16 +7631,19 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>18</v>
+      <c r="A2" t="s">
+        <v>19</v>
       </c>
       <c r="B2">
         <v>55</v>
@@ -7647,8 +7653,8 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>19</v>
+      <c r="A3" t="s">
+        <v>20</v>
       </c>
       <c r="B3">
         <v>11</v>
@@ -7669,15 +7675,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2">
         <v>233</v>
@@ -7685,7 +7691,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3">
         <v>0.7425</v>
@@ -7693,7 +7699,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4">
         <v>0.6395</v>
@@ -7701,7 +7707,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5">
         <v>0.103</v>
@@ -7709,7 +7715,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6">
         <v>0.784</v>
@@ -7717,7 +7723,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B7">
         <v>0.668</v>
@@ -7725,7 +7731,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B8">
         <v>0.3605</v>
@@ -7733,7 +7739,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9">
         <v>0.7078</v>
@@ -7741,7 +7747,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10">
         <v>0.5833</v>
@@ -7749,7 +7755,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B11">
         <v>0.8322000000000001</v>
@@ -7757,7 +7763,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12">
         <v>0.6622</v>
@@ -7765,7 +7771,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13">
         <v>0.6203</v>
@@ -7773,7 +7779,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B14">
         <v>49</v>
@@ -7781,7 +7787,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B15">
         <v>25</v>
@@ -7789,7 +7795,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B16">
         <v>35</v>
@@ -7797,7 +7803,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B17">
         <v>124</v>
@@ -7805,7 +7811,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18">
         <v>0.8333</v>
@@ -7813,7 +7819,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B19">
         <v>0.7066</v>
@@ -7821,7 +7827,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B20">
         <v>0.2833</v>
@@ -7829,7 +7835,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B21">
         <v>11</v>
@@ -7837,7 +7843,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B22">
         <v>0.6867</v>
@@ -7845,7 +7851,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B23">
         <v>0.7983</v>
@@ -7853,7 +7859,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B24">
         <v>0.7203000000000001</v>
@@ -7861,7 +7867,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B25">
         <v>0.8504</v>
@@ -7869,7 +7875,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B26">
         <v>12</v>
@@ -7877,7 +7883,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B27">
         <v>323</v>
@@ -7885,7 +7891,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B28">
         <v>36</v>
@@ -7893,7 +7899,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B29">
         <v>-0.6609</v>
@@ -7911,16 +7917,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -7928,13 +7934,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C2">
         <v>-0.367994</v>
       </c>
       <c r="D2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -7942,13 +7948,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C3">
         <v>-0.234742</v>
       </c>
       <c r="D3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -7956,13 +7962,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C4">
         <v>0.176992</v>
       </c>
       <c r="D4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -7970,13 +7976,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C5">
         <v>0.14802</v>
       </c>
       <c r="D5" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -7984,13 +7990,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C6">
         <v>0.142664</v>
       </c>
       <c r="D6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -7998,13 +8004,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C7">
         <v>-0.142597</v>
       </c>
       <c r="D7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -8012,13 +8018,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C8">
         <v>0.140167</v>
       </c>
       <c r="D8" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -8026,13 +8032,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C9">
         <v>-0.117</v>
       </c>
       <c r="D9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -8040,13 +8046,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10">
         <v>-0.113766</v>
       </c>
       <c r="D10" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -8054,13 +8060,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C11">
         <v>0.110779</v>
       </c>
       <c r="D11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -8068,13 +8074,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C12">
         <v>0.107366</v>
       </c>
       <c r="D12" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -8082,13 +8088,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C13">
         <v>0.100757</v>
       </c>
       <c r="D13" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -8096,13 +8102,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C14">
         <v>-0.100233</v>
       </c>
       <c r="D14" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -8110,13 +8116,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C15">
         <v>-0.092987</v>
       </c>
       <c r="D15" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -8124,13 +8130,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C16">
         <v>-0.081051</v>
       </c>
       <c r="D16" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -8138,13 +8144,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C17">
         <v>-0.076817</v>
       </c>
       <c r="D17" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -8152,13 +8158,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C18">
         <v>-0.076126</v>
       </c>
       <c r="D18" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -8166,13 +8172,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C19">
         <v>0.071108</v>
       </c>
       <c r="D19" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -8180,13 +8186,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C20">
         <v>-0.06943299999999999</v>
       </c>
       <c r="D20" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -8194,13 +8200,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C21">
         <v>0.056296</v>
       </c>
       <c r="D21" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -8208,13 +8214,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C22">
         <v>0.048098</v>
       </c>
       <c r="D22" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -8222,13 +8228,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C23">
         <v>0.043381</v>
       </c>
       <c r="D23" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -8236,13 +8242,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C24">
         <v>0.041768</v>
       </c>
       <c r="D24" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -8250,13 +8256,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C25">
         <v>0.040343</v>
       </c>
       <c r="D25" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -8264,13 +8270,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C26">
         <v>-0.03628</v>
       </c>
       <c r="D26" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -8278,13 +8284,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C27">
         <v>0.034714</v>
       </c>
       <c r="D27" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -8292,13 +8298,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C28">
         <v>-0.028796</v>
       </c>
       <c r="D28" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -8306,13 +8312,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C29">
         <v>0.0258</v>
       </c>
       <c r="D29" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -8320,13 +8326,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C30">
         <v>0.021674</v>
       </c>
       <c r="D30" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -8334,13 +8340,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C31">
         <v>0.021002</v>
       </c>
       <c r="D31" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -8348,13 +8354,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C32">
         <v>-0.01157</v>
       </c>
       <c r="D32" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -8362,13 +8368,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C33">
         <v>-0.010267</v>
       </c>
       <c r="D33" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -8376,13 +8382,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C34">
         <v>-0.009854</v>
       </c>
       <c r="D34" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -8390,13 +8396,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C35">
         <v>-0.009606999999999999</v>
       </c>
       <c r="D35" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -8404,13 +8410,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C36">
         <v>-0.009310000000000001</v>
       </c>
       <c r="D36" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -8418,13 +8424,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C37">
         <v>-0.001722</v>
       </c>
       <c r="D37" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -8432,13 +8438,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -8446,13 +8452,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -8460,13 +8466,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C40">
         <v>0</v>
       </c>
       <c r="D40" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -8474,13 +8480,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -8488,13 +8494,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C42">
         <v>0</v>
       </c>
       <c r="D42" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -8502,13 +8508,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -8516,13 +8522,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C44">
         <v>0</v>
       </c>
       <c r="D44" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -8530,13 +8536,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C45">
         <v>0</v>
       </c>
       <c r="D45" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -8544,13 +8550,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C46">
         <v>0</v>
       </c>
       <c r="D46" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -8558,13 +8564,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C47">
         <v>0</v>
       </c>
       <c r="D47" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -8572,13 +8578,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C48">
         <v>0</v>
       </c>
       <c r="D48" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -8586,13 +8592,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C49">
         <v>0</v>
       </c>
       <c r="D49" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -8600,13 +8606,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C50">
         <v>0</v>
       </c>
       <c r="D50" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -8614,13 +8620,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C51">
         <v>0</v>
       </c>
       <c r="D51" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -8628,13 +8634,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C52">
         <v>0</v>
       </c>
       <c r="D52" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -8642,13 +8648,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C53">
         <v>0</v>
       </c>
       <c r="D53" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -8656,13 +8662,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C54">
         <v>0</v>
       </c>
       <c r="D54" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -8670,13 +8676,13 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -8684,13 +8690,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C56">
         <v>0</v>
       </c>
       <c r="D56" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -8698,13 +8704,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C57">
         <v>0</v>
       </c>
       <c r="D57" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -8712,13 +8718,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C58">
         <v>0</v>
       </c>
       <c r="D58" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -8726,13 +8732,13 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C59">
         <v>0</v>
       </c>
       <c r="D59" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -8740,13 +8746,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -8754,13 +8760,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -8768,13 +8774,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C62">
         <v>0</v>
       </c>
       <c r="D62" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -8782,13 +8788,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C63">
         <v>0</v>
       </c>
       <c r="D63" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -8796,13 +8802,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C64">
         <v>0</v>
       </c>
       <c r="D64" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -8810,13 +8816,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C65">
         <v>0</v>
       </c>
       <c r="D65" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -8824,13 +8830,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C66">
         <v>0</v>
       </c>
       <c r="D66" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -8838,13 +8844,13 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C67">
         <v>0</v>
       </c>
       <c r="D67" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -8852,13 +8858,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C68">
         <v>0</v>
       </c>
       <c r="D68" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -8866,13 +8872,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C69">
         <v>0</v>
       </c>
       <c r="D69" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -8880,13 +8886,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C70">
         <v>0</v>
       </c>
       <c r="D70" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -8894,13 +8900,13 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C71">
         <v>0</v>
       </c>
       <c r="D71" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -8908,13 +8914,13 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -8922,13 +8928,13 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C73">
         <v>0</v>
       </c>
       <c r="D73" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -8936,13 +8942,13 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -8950,13 +8956,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C75">
         <v>0</v>
       </c>
       <c r="D75" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -8964,13 +8970,13 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C76">
         <v>0</v>
       </c>
       <c r="D76" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -8978,13 +8984,13 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C77">
         <v>0</v>
       </c>
       <c r="D77" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -8992,13 +8998,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C78">
         <v>0</v>
       </c>
       <c r="D78" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -9006,13 +9012,13 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C79">
         <v>0</v>
       </c>
       <c r="D79" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -9020,13 +9026,13 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C80">
         <v>0</v>
       </c>
       <c r="D80" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -9034,13 +9040,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C81">
         <v>0</v>
       </c>
       <c r="D81" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -9048,13 +9054,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C82">
         <v>0</v>
       </c>
       <c r="D82" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -9062,13 +9068,13 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C83">
         <v>0</v>
       </c>
       <c r="D83" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -9076,13 +9082,13 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C84">
         <v>0</v>
       </c>
       <c r="D84" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -9090,13 +9096,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C85">
         <v>0</v>
       </c>
       <c r="D85" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -9104,13 +9110,13 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C86">
         <v>0</v>
       </c>
       <c r="D86" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -9118,13 +9124,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C87">
         <v>0</v>
       </c>
       <c r="D87" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -9132,13 +9138,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C88">
         <v>0</v>
       </c>
       <c r="D88" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -9146,13 +9152,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C89">
         <v>0</v>
       </c>
       <c r="D89" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -9160,13 +9166,13 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C90">
         <v>0</v>
       </c>
       <c r="D90" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -9174,13 +9180,13 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C91">
         <v>0</v>
       </c>
       <c r="D91" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -9188,13 +9194,13 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C92">
         <v>0</v>
       </c>
       <c r="D92" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -9202,13 +9208,13 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C93">
         <v>0</v>
       </c>
       <c r="D93" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -9216,13 +9222,13 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C94">
         <v>0</v>
       </c>
       <c r="D94" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -9230,13 +9236,13 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C95">
         <v>0</v>
       </c>
       <c r="D95" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -9244,13 +9250,13 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C96">
         <v>0</v>
       </c>
       <c r="D96" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -9258,13 +9264,13 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C97">
         <v>0</v>
       </c>
       <c r="D97" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -9272,13 +9278,13 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C98">
         <v>0</v>
       </c>
       <c r="D98" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -9286,13 +9292,13 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C99">
         <v>0</v>
       </c>
       <c r="D99" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -9300,13 +9306,13 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C100">
         <v>0</v>
       </c>
       <c r="D100" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -9314,13 +9320,13 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C101">
         <v>0</v>
       </c>
       <c r="D101" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -9328,13 +9334,13 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C102">
         <v>0</v>
       </c>
       <c r="D102" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -9342,13 +9348,13 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C103">
         <v>0</v>
       </c>
       <c r="D103" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -9356,13 +9362,13 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C104">
         <v>0</v>
       </c>
       <c r="D104" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -9370,13 +9376,13 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C105">
         <v>0</v>
       </c>
       <c r="D105" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -9384,13 +9390,13 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C106">
         <v>0</v>
       </c>
       <c r="D106" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -9398,13 +9404,13 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C107">
         <v>0</v>
       </c>
       <c r="D107" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -9412,13 +9418,13 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C108">
         <v>0</v>
       </c>
       <c r="D108" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -9426,13 +9432,13 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C109">
         <v>0</v>
       </c>
       <c r="D109" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -9440,13 +9446,13 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C110">
         <v>0</v>
       </c>
       <c r="D110" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -9454,13 +9460,13 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C111">
         <v>0</v>
       </c>
       <c r="D111" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -9468,13 +9474,13 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C112">
         <v>0</v>
       </c>
       <c r="D112" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -9482,13 +9488,13 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C113">
         <v>0</v>
       </c>
       <c r="D113" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -9496,13 +9502,13 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C114">
         <v>0</v>
       </c>
       <c r="D114" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -9510,13 +9516,13 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C115">
         <v>0</v>
       </c>
       <c r="D115" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -9524,13 +9530,13 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C116">
         <v>0</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -9538,13 +9544,13 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C117">
         <v>0</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -9552,13 +9558,13 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C118">
         <v>0</v>
       </c>
       <c r="D118" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -9566,13 +9572,13 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C119">
         <v>0</v>
       </c>
       <c r="D119" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -9580,13 +9586,13 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C120">
         <v>0</v>
       </c>
       <c r="D120" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -9594,13 +9600,13 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C121">
         <v>0</v>
       </c>
       <c r="D121" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -9608,13 +9614,13 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C122">
         <v>0</v>
       </c>
       <c r="D122" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -9622,13 +9628,13 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C123">
         <v>0</v>
       </c>
       <c r="D123" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -9636,13 +9642,13 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C124">
         <v>0</v>
       </c>
       <c r="D124" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -9650,13 +9656,13 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C125">
         <v>0</v>
       </c>
       <c r="D125" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -9664,13 +9670,13 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C126">
         <v>0</v>
       </c>
       <c r="D126" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -9678,13 +9684,13 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C127">
         <v>0</v>
       </c>
       <c r="D127" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -9692,13 +9698,13 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C128">
         <v>0</v>
       </c>
       <c r="D128" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -9706,13 +9712,13 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C129">
         <v>0</v>
       </c>
       <c r="D129" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -9720,13 +9726,13 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C130">
         <v>0</v>
       </c>
       <c r="D130" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -9734,13 +9740,13 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C131">
         <v>0</v>
       </c>
       <c r="D131" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -9748,13 +9754,13 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C132">
         <v>0</v>
       </c>
       <c r="D132" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -9762,13 +9768,13 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C133">
         <v>0</v>
       </c>
       <c r="D133" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -9776,13 +9782,13 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C134">
         <v>0</v>
       </c>
       <c r="D134" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -9790,13 +9796,13 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C135">
         <v>0</v>
       </c>
       <c r="D135" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -9804,13 +9810,13 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C136">
         <v>0</v>
       </c>
       <c r="D136" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -9818,13 +9824,13 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C137">
         <v>0</v>
       </c>
       <c r="D137" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -9832,13 +9838,13 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C138">
         <v>0</v>
       </c>
       <c r="D138" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -9846,13 +9852,13 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C139">
         <v>0</v>
       </c>
       <c r="D139" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -9860,13 +9866,13 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C140">
         <v>0</v>
       </c>
       <c r="D140" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -9874,13 +9880,13 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C141">
         <v>0</v>
       </c>
       <c r="D141" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -9888,13 +9894,13 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C142">
         <v>0</v>
       </c>
       <c r="D142" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -9902,13 +9908,13 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C143">
         <v>0</v>
       </c>
       <c r="D143" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -9916,13 +9922,13 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C144">
         <v>0</v>
       </c>
       <c r="D144" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -9930,13 +9936,13 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C145">
         <v>0</v>
       </c>
       <c r="D145" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -9944,13 +9950,13 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C146">
         <v>0</v>
       </c>
       <c r="D146" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -9958,13 +9964,13 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C147">
         <v>0</v>
       </c>
       <c r="D147" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -9972,13 +9978,13 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C148">
         <v>0</v>
       </c>
       <c r="D148" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -9986,13 +9992,13 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C149">
         <v>0</v>
       </c>
       <c r="D149" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -10000,13 +10006,13 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C150">
         <v>0</v>
       </c>
       <c r="D150" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -10014,13 +10020,13 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C151">
         <v>0</v>
       </c>
       <c r="D151" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -10028,13 +10034,13 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C152">
         <v>0</v>
       </c>
       <c r="D152" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -10042,13 +10048,13 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C153">
         <v>0</v>
       </c>
       <c r="D153" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -10056,13 +10062,13 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C154">
         <v>0</v>
       </c>
       <c r="D154" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -10070,13 +10076,13 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C155">
         <v>0</v>
       </c>
       <c r="D155" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -10084,13 +10090,13 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C156">
         <v>0</v>
       </c>
       <c r="D156" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -10098,13 +10104,13 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C157">
         <v>0</v>
       </c>
       <c r="D157" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -10112,13 +10118,13 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C158">
         <v>0</v>
       </c>
       <c r="D158" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -10126,13 +10132,13 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C159">
         <v>0</v>
       </c>
       <c r="D159" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -10140,13 +10146,13 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C160">
         <v>0</v>
       </c>
       <c r="D160" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -10154,13 +10160,13 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C161">
         <v>0</v>
       </c>
       <c r="D161" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -10168,13 +10174,13 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C162">
         <v>0</v>
       </c>
       <c r="D162" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -10182,13 +10188,13 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C163">
         <v>0</v>
       </c>
       <c r="D163" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -10196,13 +10202,13 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C164">
         <v>0</v>
       </c>
       <c r="D164" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -10210,13 +10216,13 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C165">
         <v>0</v>
       </c>
       <c r="D165" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -10224,13 +10230,13 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C166">
         <v>0</v>
       </c>
       <c r="D166" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -10238,13 +10244,13 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C167">
         <v>0</v>
       </c>
       <c r="D167" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -10252,13 +10258,13 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C168">
         <v>0</v>
       </c>
       <c r="D168" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -10266,13 +10272,13 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C169">
         <v>0</v>
       </c>
       <c r="D169" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -10280,13 +10286,13 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C170">
         <v>0</v>
       </c>
       <c r="D170" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -10294,13 +10300,13 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C171">
         <v>0</v>
       </c>
       <c r="D171" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -10308,13 +10314,13 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C172">
         <v>0</v>
       </c>
       <c r="D172" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -10322,13 +10328,13 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C173">
         <v>0</v>
       </c>
       <c r="D173" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -10336,13 +10342,13 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C174">
         <v>0</v>
       </c>
       <c r="D174" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -10350,13 +10356,13 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C175">
         <v>0</v>
       </c>
       <c r="D175" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -10364,13 +10370,13 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C176">
         <v>0</v>
       </c>
       <c r="D176" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -10378,13 +10384,13 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C177">
         <v>0</v>
       </c>
       <c r="D177" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -10392,13 +10398,13 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C178">
         <v>0</v>
       </c>
       <c r="D178" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -10406,13 +10412,13 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C179">
         <v>0</v>
       </c>
       <c r="D179" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -10420,13 +10426,13 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C180">
         <v>0</v>
       </c>
       <c r="D180" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -10434,13 +10440,13 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C181">
         <v>0</v>
       </c>
       <c r="D181" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -10448,13 +10454,13 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C182">
         <v>0</v>
       </c>
       <c r="D182" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -10462,13 +10468,13 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C183">
         <v>0</v>
       </c>
       <c r="D183" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -10476,13 +10482,13 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C184">
         <v>0</v>
       </c>
       <c r="D184" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -10490,13 +10496,13 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C185">
         <v>0</v>
       </c>
       <c r="D185" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -10504,13 +10510,13 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C186">
         <v>0</v>
       </c>
       <c r="D186" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -10518,13 +10524,13 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C187">
         <v>0</v>
       </c>
       <c r="D187" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -10532,13 +10538,13 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C188">
         <v>0</v>
       </c>
       <c r="D188" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -10546,13 +10552,13 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C189">
         <v>0</v>
       </c>
       <c r="D189" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -10560,13 +10566,13 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C190">
         <v>0</v>
       </c>
       <c r="D190" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -10574,13 +10580,13 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C191">
         <v>0</v>
       </c>
       <c r="D191" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -10588,13 +10594,13 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C192">
         <v>0</v>
       </c>
       <c r="D192" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -10602,13 +10608,13 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C193">
         <v>0</v>
       </c>
       <c r="D193" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -10616,13 +10622,13 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C194">
         <v>0</v>
       </c>
       <c r="D194" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -10630,13 +10636,13 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C195">
         <v>0</v>
       </c>
       <c r="D195" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -10644,13 +10650,13 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C196">
         <v>0</v>
       </c>
       <c r="D196" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -10658,13 +10664,13 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C197">
         <v>0</v>
       </c>
       <c r="D197" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -10672,13 +10678,13 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C198">
         <v>0</v>
       </c>
       <c r="D198" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -10686,13 +10692,13 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C199">
         <v>0</v>
       </c>
       <c r="D199" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -10700,13 +10706,13 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C200">
         <v>0</v>
       </c>
       <c r="D200" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -10714,13 +10720,13 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C201">
         <v>0</v>
       </c>
       <c r="D201" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -10728,13 +10734,13 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C202">
         <v>0</v>
       </c>
       <c r="D202" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -10742,13 +10748,13 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C203">
         <v>0</v>
       </c>
       <c r="D203" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -10756,13 +10762,13 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C204">
         <v>0</v>
       </c>
       <c r="D204" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -10770,13 +10776,13 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C205">
         <v>0</v>
       </c>
       <c r="D205" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -10784,13 +10790,13 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C206">
         <v>0</v>
       </c>
       <c r="D206" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -10798,13 +10804,13 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C207">
         <v>0</v>
       </c>
       <c r="D207" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -10812,13 +10818,13 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C208">
         <v>0</v>
       </c>
       <c r="D208" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -10826,13 +10832,13 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C209">
         <v>0</v>
       </c>
       <c r="D209" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -10840,13 +10846,13 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C210">
         <v>0</v>
       </c>
       <c r="D210" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -10854,13 +10860,13 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C211">
         <v>0</v>
       </c>
       <c r="D211" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -10868,13 +10874,13 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C212">
         <v>0</v>
       </c>
       <c r="D212" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -10882,13 +10888,13 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C213">
         <v>0</v>
       </c>
       <c r="D213" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -10896,13 +10902,13 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C214">
         <v>0</v>
       </c>
       <c r="D214" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -10910,13 +10916,13 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C215">
         <v>0</v>
       </c>
       <c r="D215" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -10924,13 +10930,13 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C216">
         <v>0</v>
       </c>
       <c r="D216" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -10938,13 +10944,13 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C217">
         <v>0</v>
       </c>
       <c r="D217" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -10952,13 +10958,13 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C218">
         <v>0</v>
       </c>
       <c r="D218" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -10966,13 +10972,13 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C219">
         <v>0</v>
       </c>
       <c r="D219" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -10980,13 +10986,13 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C220">
         <v>0</v>
       </c>
       <c r="D220" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -10994,13 +11000,13 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C221">
         <v>0</v>
       </c>
       <c r="D221" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -11008,13 +11014,13 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C222">
         <v>0</v>
       </c>
       <c r="D222" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -11022,13 +11028,13 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C223">
         <v>0</v>
       </c>
       <c r="D223" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -11036,13 +11042,13 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C224">
         <v>0</v>
       </c>
       <c r="D224" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -11050,13 +11056,13 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C225">
         <v>0</v>
       </c>
       <c r="D225" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -11064,13 +11070,13 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C226">
         <v>0</v>
       </c>
       <c r="D226" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -11078,13 +11084,13 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C227">
         <v>0</v>
       </c>
       <c r="D227" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -11092,13 +11098,13 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C228">
         <v>0</v>
       </c>
       <c r="D228" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -11106,13 +11112,13 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C229">
         <v>0</v>
       </c>
       <c r="D229" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -11120,13 +11126,13 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C230">
         <v>0</v>
       </c>
       <c r="D230" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -11134,13 +11140,13 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C231">
         <v>0</v>
       </c>
       <c r="D231" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -11148,13 +11154,13 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C232">
         <v>0</v>
       </c>
       <c r="D232" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -11162,13 +11168,13 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C233">
         <v>0</v>
       </c>
       <c r="D233" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -11176,13 +11182,13 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C234">
         <v>0</v>
       </c>
       <c r="D234" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -11190,13 +11196,13 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C235">
         <v>0</v>
       </c>
       <c r="D235" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -11204,13 +11210,13 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C236">
         <v>0</v>
       </c>
       <c r="D236" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -11218,13 +11224,13 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C237">
         <v>0</v>
       </c>
       <c r="D237" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -11232,13 +11238,13 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C238">
         <v>0</v>
       </c>
       <c r="D238" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -11246,13 +11252,13 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C239">
         <v>0</v>
       </c>
       <c r="D239" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -11260,13 +11266,13 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C240">
         <v>0</v>
       </c>
       <c r="D240" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -11274,13 +11280,13 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C241">
         <v>0</v>
       </c>
       <c r="D241" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -11288,13 +11294,13 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C242">
         <v>0</v>
       </c>
       <c r="D242" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -11302,13 +11308,13 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C243">
         <v>0</v>
       </c>
       <c r="D243" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -11316,13 +11322,13 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C244">
         <v>0</v>
       </c>
       <c r="D244" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -11330,13 +11336,13 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C245">
         <v>0</v>
       </c>
       <c r="D245" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -11344,13 +11350,13 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C246">
         <v>0</v>
       </c>
       <c r="D246" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -11358,13 +11364,13 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C247">
         <v>0</v>
       </c>
       <c r="D247" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -11372,13 +11378,13 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C248">
         <v>0</v>
       </c>
       <c r="D248" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -11386,13 +11392,13 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C249">
         <v>0</v>
       </c>
       <c r="D249" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -11400,13 +11406,13 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C250">
         <v>0</v>
       </c>
       <c r="D250" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -11414,13 +11420,13 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C251">
         <v>0</v>
       </c>
       <c r="D251" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -11428,13 +11434,13 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C252">
         <v>0</v>
       </c>
       <c r="D252" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -11442,13 +11448,13 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C253">
         <v>0</v>
       </c>
       <c r="D253" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -11456,13 +11462,13 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C254">
         <v>0</v>
       </c>
       <c r="D254" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -11470,13 +11476,13 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C255">
         <v>0</v>
       </c>
       <c r="D255" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -11484,13 +11490,13 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C256">
         <v>0</v>
       </c>
       <c r="D256" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -11498,13 +11504,13 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C257">
         <v>0</v>
       </c>
       <c r="D257" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -11512,13 +11518,13 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C258">
         <v>0</v>
       </c>
       <c r="D258" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -11526,13 +11532,13 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C259">
         <v>0</v>
       </c>
       <c r="D259" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -11540,13 +11546,13 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C260">
         <v>0</v>
       </c>
       <c r="D260" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -11554,13 +11560,13 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C261">
         <v>0</v>
       </c>
       <c r="D261" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -11568,13 +11574,13 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C262">
         <v>0</v>
       </c>
       <c r="D262" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -11582,13 +11588,13 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C263">
         <v>0</v>
       </c>
       <c r="D263" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -11596,13 +11602,13 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C264">
         <v>0</v>
       </c>
       <c r="D264" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -11610,13 +11616,13 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C265">
         <v>0</v>
       </c>
       <c r="D265" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -11624,13 +11630,13 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C266">
         <v>0</v>
       </c>
       <c r="D266" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -11638,13 +11644,13 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C267">
         <v>0</v>
       </c>
       <c r="D267" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -11652,13 +11658,13 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C268">
         <v>0</v>
       </c>
       <c r="D268" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -11666,13 +11672,13 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C269">
         <v>0</v>
       </c>
       <c r="D269" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -11680,13 +11686,13 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C270">
         <v>0</v>
       </c>
       <c r="D270" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -11694,13 +11700,13 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C271">
         <v>0</v>
       </c>
       <c r="D271" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -11708,13 +11714,13 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C272">
         <v>0</v>
       </c>
       <c r="D272" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -11722,13 +11728,13 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C273">
         <v>0</v>
       </c>
       <c r="D273" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -11736,13 +11742,13 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C274">
         <v>0</v>
       </c>
       <c r="D274" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -11750,13 +11756,13 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C275">
         <v>0</v>
       </c>
       <c r="D275" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -11764,13 +11770,13 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C276">
         <v>0</v>
       </c>
       <c r="D276" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -11778,13 +11784,13 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C277">
         <v>0</v>
       </c>
       <c r="D277" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -11792,13 +11798,13 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C278">
         <v>0</v>
       </c>
       <c r="D278" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -11806,13 +11812,13 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C279">
         <v>0</v>
       </c>
       <c r="D279" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -11820,13 +11826,13 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C280">
         <v>0</v>
       </c>
       <c r="D280" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -11834,13 +11840,13 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C281">
         <v>0</v>
       </c>
       <c r="D281" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -11848,13 +11854,13 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C282">
         <v>0</v>
       </c>
       <c r="D282" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -11862,13 +11868,13 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C283">
         <v>0</v>
       </c>
       <c r="D283" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -11876,13 +11882,13 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C284">
         <v>0</v>
       </c>
       <c r="D284" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -11890,13 +11896,13 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C285">
         <v>0</v>
       </c>
       <c r="D285" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -11904,13 +11910,13 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C286">
         <v>0</v>
       </c>
       <c r="D286" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -11918,13 +11924,13 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C287">
         <v>0</v>
       </c>
       <c r="D287" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -11932,13 +11938,13 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C288">
         <v>0</v>
       </c>
       <c r="D288" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -11946,13 +11952,13 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C289">
         <v>0</v>
       </c>
       <c r="D289" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -11960,13 +11966,13 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C290">
         <v>0</v>
       </c>
       <c r="D290" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -11974,13 +11980,13 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C291">
         <v>0</v>
       </c>
       <c r="D291" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -11988,13 +11994,13 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C292">
         <v>0</v>
       </c>
       <c r="D292" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -12002,13 +12008,13 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C293">
         <v>0</v>
       </c>
       <c r="D293" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -12016,13 +12022,13 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C294">
         <v>0</v>
       </c>
       <c r="D294" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -12030,13 +12036,13 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C295">
         <v>0</v>
       </c>
       <c r="D295" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -12044,13 +12050,13 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C296">
         <v>0</v>
       </c>
       <c r="D296" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -12058,13 +12064,13 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C297">
         <v>0</v>
       </c>
       <c r="D297" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -12072,13 +12078,13 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C298">
         <v>0</v>
       </c>
       <c r="D298" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -12086,13 +12092,13 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C299">
         <v>0</v>
       </c>
       <c r="D299" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -12100,13 +12106,13 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C300">
         <v>0</v>
       </c>
       <c r="D300" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -12114,13 +12120,13 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C301">
         <v>0</v>
       </c>
       <c r="D301" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -12128,13 +12134,13 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C302">
         <v>0</v>
       </c>
       <c r="D302" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -12142,13 +12148,13 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C303">
         <v>0</v>
       </c>
       <c r="D303" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -12156,13 +12162,13 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C304">
         <v>0</v>
       </c>
       <c r="D304" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -12170,13 +12176,13 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C305">
         <v>0</v>
       </c>
       <c r="D305" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -12184,13 +12190,13 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C306">
         <v>0</v>
       </c>
       <c r="D306" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -12198,13 +12204,13 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C307">
         <v>0</v>
       </c>
       <c r="D307" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -12212,13 +12218,13 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C308">
         <v>0</v>
       </c>
       <c r="D308" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -12226,13 +12232,13 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C309">
         <v>0</v>
       </c>
       <c r="D309" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -12240,13 +12246,13 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C310">
         <v>0</v>
       </c>
       <c r="D310" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -12254,13 +12260,13 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C311">
         <v>0</v>
       </c>
       <c r="D311" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -12268,13 +12274,13 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C312">
         <v>0</v>
       </c>
       <c r="D312" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -12282,13 +12288,13 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C313">
         <v>0</v>
       </c>
       <c r="D313" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -12296,13 +12302,13 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C314">
         <v>0</v>
       </c>
       <c r="D314" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -12310,13 +12316,13 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C315">
         <v>0</v>
       </c>
       <c r="D315" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -12324,13 +12330,13 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C316">
         <v>0</v>
       </c>
       <c r="D316" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -12338,13 +12344,13 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C317">
         <v>0</v>
       </c>
       <c r="D317" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -12352,13 +12358,13 @@
         <v>317</v>
       </c>
       <c r="B318" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C318">
         <v>0</v>
       </c>
       <c r="D318" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -12366,13 +12372,13 @@
         <v>318</v>
       </c>
       <c r="B319" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C319">
         <v>0</v>
       </c>
       <c r="D319" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -12380,13 +12386,13 @@
         <v>319</v>
       </c>
       <c r="B320" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C320">
         <v>0</v>
       </c>
       <c r="D320" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -12394,13 +12400,13 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C321">
         <v>0</v>
       </c>
       <c r="D321" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -12408,13 +12414,13 @@
         <v>321</v>
       </c>
       <c r="B322" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C322">
         <v>0</v>
       </c>
       <c r="D322" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -12422,13 +12428,13 @@
         <v>322</v>
       </c>
       <c r="B323" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C323">
         <v>0</v>
       </c>
       <c r="D323" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -12436,13 +12442,13 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C324">
         <v>0</v>
       </c>
       <c r="D324" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -12457,19 +12463,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2" spans="1:5">
